--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T18:22:17+00:00</t>
+    <t>2025-11-28T16:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T16:27:44+00:00</t>
+    <t>2025-12-09T10:41:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T10:41:43+00:00</t>
+    <t>2025-12-09T13:35:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T13:35:37+00:00</t>
+    <t>2025-12-09T14:49:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T14:49:30+00:00</t>
+    <t>2025-12-10T08:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-10T08:51:21+00:00</t>
+    <t>2025-12-10T14:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-10T14:21:49+00:00</t>
+    <t>2025-12-15T13:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T13:43:12+00:00</t>
+    <t>2025-12-16T11:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T11:22:18+00:00</t>
+    <t>2025-12-16T14:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:14:47+00:00</t>
+    <t>2025-12-16T15:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T15:47:53+00:00</t>
+    <t>2025-12-16T16:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T16:52:49+00:00</t>
+    <t>2025-12-17T15:53:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-jdv-tre-r221-modele-document-cda-non-structure-all.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T15:53:11+00:00</t>
+    <t>2025-12-18T13:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
